--- a/data/atlantic_salmon/params/Population.xlsx
+++ b/data/atlantic_salmon/params/Population.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\local_to_global_mariculture_modelling\data\atlantic_salmon\params\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53878AB0-13F3-4C29-BA3F-B3FB928ABC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FBB6F8-FD50-4EAC-80CE-12A0BB379F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12528" yWindow="2340" windowWidth="21540" windowHeight="12120" xr2:uid="{480EBA47-7647-41F2-86F2-E9AC7A875918}"/>
+    <workbookView xWindow="7224" yWindow="876" windowWidth="30744" windowHeight="15132" xr2:uid="{480EBA47-7647-41F2-86F2-E9AC7A875918}"/>
   </bookViews>
   <sheets>
     <sheet name="Population" sheetId="1" r:id="rId1"/>
@@ -1067,7 +1067,7 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>5000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
